--- a/Output/PowerPoint_Figures/Fig_7/Fig_7d_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_7/Fig_7d_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,44 +417,44 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Drug</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Predicted_Heart_Damage_pct</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Actual_Heart_Damage</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>is_positive</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Threshold_Value</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Threshold_Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -485,7 +473,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -493,12 +481,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,7 +505,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -525,12 +513,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>16</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,7 +537,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -557,12 +545,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -581,7 +569,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -589,12 +577,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -613,7 +601,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -621,12 +609,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -645,7 +633,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -653,12 +641,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -677,7 +665,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -685,12 +673,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>17</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -709,7 +697,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -717,12 +705,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -741,7 +729,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -749,12 +737,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -773,7 +761,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -781,12 +769,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -805,7 +793,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -813,12 +801,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>18</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -837,7 +825,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -845,12 +833,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -877,12 +865,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -901,7 +889,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -909,12 +897,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -933,7 +921,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -941,12 +929,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -965,7 +953,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -973,12 +961,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -997,7 +985,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1005,12 +993,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1029,7 +1017,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1037,12 +1025,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>14</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1061,7 +1049,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1069,12 +1057,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1093,7 +1081,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1101,12 +1089,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1125,7 +1113,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1133,12 +1121,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1157,7 +1145,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1165,12 +1153,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1189,7 +1177,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1197,12 +1185,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>8</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1221,7 +1209,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1229,12 +1217,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1253,7 +1241,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\heart_damage_predictions.csv</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/heart_damage_predictions.csv</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -1261,7 +1249,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Output\Prediction_Scatter_Data\prediction_thresholds.json</t>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Output/Prediction_Scatter_Data/prediction_thresholds.json</t>
         </is>
       </c>
     </row>
